--- a/src/assets/applicants.xlsx
+++ b/src/assets/applicants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>First Name</t>
   </si>
@@ -89,6 +89,31 @@
   </si>
   <si>
     <t>3hrs</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>j@gmail.com</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfect 👌 here’s a polished 250-word job application response you can adapt:
+⸻
+I am deeply interested in this opportunity because it aligns closely with both my professional goals and personal values. Over the course of my career, I have consistently sought roles that allow me to grow while making a tangible impact. This position represents exactly that—a chance to contribute my skills in a meaningful way while continuing to learn and evolve in a dynamic environment.
+What excites me most about this role is the balance between challenge and growth. I thrive in environments where I can tackle complex problems, collaborate with diverse teams, and see the direct results of my contributions. The chance to work within an organization that values innovation, creativity, and continuous improvement is particularly motivating for me. I am eager to bring not only my technical expertise and problem-solving abilities but also my dedication to teamwork and adaptability.
+Additionally, this role aligns with my long-term vision of developing into a well-rounded professional who can bridge both technical execution and strategic thinking. I believe this opportunity will push me to refine my strengths while gaining exposure to new skills that will be vital for my career. More importantly, I see it as a platform where I can create value, support organizational goals, and grow alongside the company’s success.
+In summary, my interest in this role stems from its potential to challenge me, allow me to contribute meaningfully, and help me become a stronger professional over time.
+⸻
+Do you want me to make it sound more formal and corporate (like for a big company) or more approachable and personal (like for a startup)?</t>
+  </si>
+  <si>
+    <t>mone</t>
+  </si>
+  <si>
+    <t>4 hours</t>
   </si>
 </sst>
 </file>
@@ -465,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -574,6 +599,38 @@
         <v>19</v>
       </c>
     </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
